--- a/data/obx_xlsx/ENDUR.OL.xlsx
+++ b/data/obx_xlsx/ENDUR.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="448">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -826,6 +826,9 @@
   </si>
   <si>
     <t>Total current liabilities</t>
+  </si>
+  <si>
+    <t>Loans and borrowings (Do not use)</t>
   </si>
   <si>
     <t>Convertible Loan</t>
@@ -1485,7 +1488,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1563,6 +1566,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2765,7 +2771,8 @@
         <v>133.7</v>
       </c>
       <c r="E29" s="16">
-        <v>142.4</v>
+        <f>SUM(E30:E36)</f>
+        <v>119.6</v>
       </c>
       <c r="F29" s="15">
         <v>52.9</v>
@@ -2773,8 +2780,9 @@
       <c r="G29" s="15">
         <v>8.22</v>
       </c>
-      <c r="H29" s="15">
-        <v>25.08</v>
+      <c r="H29" s="16">
+        <f>SUM(H30:H36)</f>
+        <v>4.08</v>
       </c>
       <c r="I29" s="15">
         <v>4.14</v>
@@ -2786,7 +2794,8 @@
         <v>6.86</v>
       </c>
       <c r="L29" s="16">
-        <v>186.11</v>
+        <f>SUM(L30:L36)</f>
+        <v>20.37</v>
       </c>
       <c r="M29" s="16">
         <v>104.0</v>
@@ -2794,11 +2803,26 @@
       <c r="N29" s="16">
         <v>336.73</v>
       </c>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
+      <c r="O29" s="16">
+        <f t="shared" ref="O29:S29" si="1">SUM(O30:O36)</f>
+        <v>57.38</v>
+      </c>
+      <c r="P29" s="16">
+        <f t="shared" si="1"/>
+        <v>55.54</v>
+      </c>
+      <c r="Q29" s="16">
+        <f t="shared" si="1"/>
+        <v>176.76</v>
+      </c>
+      <c r="R29" s="16">
+        <f t="shared" si="1"/>
+        <v>34.91</v>
+      </c>
+      <c r="S29" s="16">
+        <f t="shared" si="1"/>
+        <v>75.83</v>
+      </c>
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
@@ -10050,10 +10074,22 @@
       <c r="O66" s="16">
         <v>734.85</v>
       </c>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="14"/>
-      <c r="R66" s="14"/>
-      <c r="S66" s="14"/>
+      <c r="P66" s="14">
+        <f t="shared" ref="P66:Q66" si="1">SUM(P89,P92)</f>
+        <v>875.09</v>
+      </c>
+      <c r="Q66" s="14">
+        <f t="shared" si="1"/>
+        <v>910.49</v>
+      </c>
+      <c r="R66" s="14">
+        <f t="shared" ref="R66:S66" si="2">SUM(R67,R70,R73,R84)</f>
+        <v>829.19</v>
+      </c>
+      <c r="S66" s="14">
+        <f t="shared" si="2"/>
+        <v>265.52</v>
+      </c>
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="13" t="s">
@@ -11991,8 +12027,8 @@
       </c>
     </row>
     <row r="122" ht="15.0" customHeight="1">
-      <c r="A122" s="13" t="s">
-        <v>262</v>
+      <c r="A122" s="26" t="s">
+        <v>269</v>
       </c>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -12039,7 +12075,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -12064,7 +12100,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -12092,8 +12128,8 @@
       <c r="S124" s="14"/>
     </row>
     <row r="125" ht="15.0" customHeight="1">
-      <c r="A125" s="13" t="s">
-        <v>262</v>
+      <c r="A125" s="26" t="s">
+        <v>269</v>
       </c>
       <c r="B125" s="16">
         <v>541.1</v>
@@ -12138,7 +12174,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B126" s="16">
         <v>230.3</v>
@@ -12179,7 +12215,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -12204,7 +12240,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -12245,7 +12281,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B129" s="15">
         <v>61.1</v>
@@ -12298,7 +12334,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B130" s="15">
         <v>70.8</v>
@@ -12337,7 +12373,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -12362,7 +12398,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B132" s="14"/>
       <c r="C132" s="19">
@@ -12397,7 +12433,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B133" s="18">
         <v>903.3</v>
@@ -12456,7 +12492,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -12481,7 +12517,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B135" s="15">
         <v>0.1</v>
@@ -12514,7 +12550,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B136" s="18">
         <v>1821.7</v>
@@ -12573,7 +12609,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B137" s="15">
         <v>18.3</v>
@@ -12632,7 +12668,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B138" s="16">
         <v>1214.0</v>
@@ -12659,7 +12695,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B139" s="15">
         <v>7.7</v>
@@ -12708,7 +12744,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B140" s="19">
         <v>-0.1</v>
@@ -12745,7 +12781,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B141" s="16">
         <v>1162.7</v>
@@ -12794,7 +12830,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B142" s="15">
         <v>28.8</v>
@@ -12845,7 +12881,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B143" s="15">
         <v>14.7</v>
@@ -12874,7 +12910,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B144" s="15">
         <v>0.2</v>
@@ -12899,7 +12935,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -12932,7 +12968,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -12961,7 +12997,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -12992,7 +13028,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B148" s="18">
         <v>1232.3</v>
@@ -13090,7 +13126,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B150" s="14"/>
       <c r="C150" s="19">
@@ -13115,7 +13151,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B151" s="21">
         <v>2.1</v>
@@ -13146,7 +13182,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B152" s="18">
         <v>1234.4</v>
@@ -13205,7 +13241,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B153" s="14"/>
       <c r="C153" s="15">
@@ -13238,7 +13274,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B154" s="18">
         <v>3056.1</v>
@@ -13297,7 +13333,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B155" s="15">
         <v>36.68</v>
@@ -13356,7 +13392,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B156" s="15">
         <v>0.21</v>
@@ -13415,7 +13451,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B157" s="15">
         <v>36.89</v>
@@ -13474,7 +13510,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -13501,7 +13537,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -13528,7 +13564,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -13555,7 +13591,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -13582,7 +13618,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -13609,7 +13645,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -13636,7 +13672,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -13663,7 +13699,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B165" s="16">
         <v>378.7</v>
@@ -13696,7 +13732,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B166" s="16">
         <v>117.7</v>
@@ -13729,7 +13765,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B167" s="16">
         <v>243.9</v>
@@ -13762,7 +13798,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B168" s="15">
         <v>17.0</v>
@@ -13795,7 +13831,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B169" s="15">
         <v>0.1</v>
@@ -13822,7 +13858,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B170" s="15">
         <v>36.89</v>
@@ -13881,7 +13917,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B171" s="15">
         <v>0.21</v>
@@ -13940,7 +13976,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B172" s="15">
         <v>36.68</v>
@@ -13999,7 +14035,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B173" s="15">
         <v>1.0</v>
@@ -14058,7 +14094,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B174" s="16">
         <v>767.0</v>
@@ -14099,7 +14135,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -14130,7 +14166,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -14161,7 +14197,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -14192,7 +14228,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -14223,7 +14259,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B179" s="16">
         <v>3255.0</v>
@@ -14260,7 +14296,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B180" s="16">
         <v>4784.0</v>
@@ -15145,7 +15181,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15479,63 +15515,63 @@
         <v>40</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -15676,7 +15712,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -15703,7 +15739,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -15730,7 +15766,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -15761,7 +15797,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -15814,7 +15850,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B24" s="15">
         <v>11.6</v>
@@ -15861,7 +15897,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B25" s="19">
         <v>-5.1</v>
@@ -15886,7 +15922,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -15911,7 +15947,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B27" s="16">
         <v>178.8</v>
@@ -15940,7 +15976,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B28" s="15">
         <v>42.4</v>
@@ -15971,7 +16007,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -15998,7 +16034,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B30" s="15">
         <v>0.4</v>
@@ -16027,7 +16063,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B31" s="19">
         <v>-2.6</v>
@@ -16072,7 +16108,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B32" s="15">
         <v>1.8</v>
@@ -16105,7 +16141,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -16134,7 +16170,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -16159,7 +16195,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="19">
@@ -16198,7 +16234,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -16225,7 +16261,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -16254,7 +16290,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -16281,7 +16317,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B39" s="19">
         <v>-5.7</v>
@@ -16310,7 +16346,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" s="15">
         <v>97.2</v>
@@ -16339,7 +16375,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -16437,7 +16473,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -16597,7 +16633,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B47" s="15">
         <v>62.5</v>
@@ -16628,7 +16664,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -16657,7 +16693,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14">
@@ -16684,7 +16720,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -16733,7 +16769,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -16758,7 +16794,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -16783,7 +16819,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -16808,7 +16844,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -16843,7 +16879,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B55" s="18">
         <v>493.6</v>
@@ -16902,7 +16938,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B56" s="15">
         <v>15.1</v>
@@ -16943,7 +16979,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B57" s="19">
         <v>-58.3</v>
@@ -17000,7 +17036,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -17029,7 +17065,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -17058,7 +17094,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -17089,7 +17125,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -17122,7 +17158,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -17151,7 +17187,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B63" s="19">
         <v>-20.2</v>
@@ -17176,7 +17212,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -17207,7 +17243,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -17234,7 +17270,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -17263,7 +17299,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -17292,7 +17328,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -17319,7 +17355,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -17344,7 +17380,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -17369,7 +17405,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B71" s="15">
         <v>3.3</v>
@@ -17394,7 +17430,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B72" s="19">
         <v>-10.3</v>
@@ -17429,7 +17465,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B73" s="19">
         <v>-11.3</v>
@@ -17454,7 +17490,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="24">
@@ -17485,7 +17521,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14">
@@ -17512,7 +17548,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B76" s="22">
         <v>-81.7</v>
@@ -17571,7 +17607,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B77" s="15">
         <v>2.5</v>
@@ -17612,7 +17648,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B78" s="14">
         <v>0.0</v>
@@ -17669,7 +17705,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B79" s="19">
         <v>-88.0</v>
@@ -17708,7 +17744,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -17733,7 +17769,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B81" s="24">
         <v>-119.6</v>
@@ -17762,7 +17798,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B82" s="19">
         <v>-96.8</v>
@@ -17797,7 +17833,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B83" s="14"/>
       <c r="C83" s="14">
@@ -17852,7 +17888,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -17877,7 +17913,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -17912,7 +17948,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -17945,7 +17981,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B87" s="19">
         <v>-11.4</v>
@@ -17974,7 +18010,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B88" s="19">
         <v>-0.1</v>
@@ -18001,7 +18037,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B89" s="23">
         <v>-313.4</v>
@@ -18060,7 +18096,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B90" s="16">
         <v>103.2</v>
@@ -18119,7 +18155,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B91" s="16">
         <v>192.5</v>
@@ -18178,7 +18214,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B92" s="19">
         <v>-9.4</v>
@@ -18209,7 +18245,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B93" s="15">
         <v>89.2</v>
@@ -18238,7 +18274,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -18269,7 +18305,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B95" s="21">
         <v>89.1</v>
@@ -18328,7 +18364,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B96" s="15">
         <v>15.2</v>
@@ -19285,7 +19321,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19675,7 +19711,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -19756,1920 +19792,1920 @@
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
+      <c r="A19" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="29" t="s">
+        <v>400</v>
+      </c>
+      <c r="B20" s="30">
         <v>3372.02</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>2319.62</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>1543.55</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>1638.81</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>1111.25</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="30">
         <v>323.14</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="30">
         <v>128.69</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="30">
         <v>124.01</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="30">
         <v>109.33</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="31">
         <v>95.27</v>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="30">
         <v>231.2</v>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="30">
         <v>1045.1</v>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="30">
         <v>1441.05</v>
       </c>
-      <c r="O20" s="29">
+      <c r="O20" s="30">
         <v>1198.46</v>
       </c>
-      <c r="P20" s="29">
+      <c r="P20" s="30">
         <v>860.96</v>
       </c>
-      <c r="Q20" s="29">
+      <c r="Q20" s="30">
         <v>1478.88</v>
       </c>
-      <c r="R20" s="29">
+      <c r="R20" s="30">
         <v>1195.46</v>
       </c>
-      <c r="S20" s="31"/>
+      <c r="S20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="B21" s="30">
         <v>1997.05</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>1387.28</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>949.09</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>665.18</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>359.28</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>156.09</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>137.7</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>320.98</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>584.39</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>802.22</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="30">
         <v>955.35</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>1204.89</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>1234.96</v>
       </c>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
+      <c r="A22" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="A23" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="B23" s="30">
         <v>2560.32</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <v>1397.22</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>946.85</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>939.61</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>893.85</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>247.73</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>115.61</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="30">
         <v>177.58</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="30">
         <v>125.5</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="31">
         <v>62.44</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="30">
         <v>116.39</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="30">
         <v>210.96</v>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="30">
         <v>348.58</v>
       </c>
-      <c r="O23" s="29">
+      <c r="O23" s="30">
         <v>299.47</v>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="30">
         <v>532.26</v>
       </c>
-      <c r="Q23" s="29">
+      <c r="Q23" s="30">
         <v>293.6</v>
       </c>
-      <c r="R23" s="29">
+      <c r="R23" s="30">
         <v>260.61</v>
       </c>
-      <c r="S23" s="31"/>
+      <c r="S23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="B24" s="30">
         <v>1347.57</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>885.05</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>628.73</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>474.88</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>312.05</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>145.77</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>119.5</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>138.58</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>172.77</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>207.57</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="30">
         <v>301.53</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>336.98</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>346.9</v>
       </c>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
+      <c r="A25" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="B26" s="30">
+      <c r="A26" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="B26" s="31">
         <v>69.4</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <v>38.0</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <v>34.49</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <v>34.45</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <v>61.0</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="31">
         <v>58.25</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="31">
         <v>61.5</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="31">
         <v>94.5</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="31">
         <v>96.5</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="31">
         <v>50.13</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="31">
         <v>93.44</v>
       </c>
-      <c r="M26" s="29">
+      <c r="M26" s="30">
         <v>169.36</v>
       </c>
-      <c r="N26" s="29">
+      <c r="N26" s="30">
         <v>279.83</v>
       </c>
-      <c r="O26" s="29">
+      <c r="O26" s="30">
         <v>240.41</v>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="30">
         <v>427.29</v>
       </c>
-      <c r="Q26" s="29">
+      <c r="Q26" s="30">
         <v>297.35</v>
       </c>
-      <c r="R26" s="29">
+      <c r="R26" s="30">
         <v>276.43</v>
       </c>
-      <c r="S26" s="29">
+      <c r="S26" s="30">
         <v>1751.99</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="B27" s="31">
         <v>47.47</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>45.24</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>49.94</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>61.94</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>74.35</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>72.18</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <v>79.21</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="30">
         <v>100.78</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="30">
         <v>137.85</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="30">
         <v>166.63</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="30">
         <v>242.07</v>
       </c>
-      <c r="M27" s="29">
+      <c r="M27" s="30">
         <v>282.85</v>
       </c>
-      <c r="N27" s="29">
+      <c r="N27" s="30">
         <v>304.26</v>
       </c>
-      <c r="O27" s="29">
+      <c r="O27" s="30">
         <v>598.69</v>
       </c>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>406</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
+      <c r="A28" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>407</v>
-      </c>
-      <c r="B29" s="32">
+      <c r="A29" s="29" t="s">
+        <v>408</v>
+      </c>
+      <c r="B29" s="33">
         <v>13.39</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="33">
         <v>0.12</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="33">
         <v>14.8</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <v>-33.34</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="34">
         <v>-11.38</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="34">
         <v>-16.67</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="33">
         <v>1.41</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="33">
         <v>4.57</v>
       </c>
-      <c r="J29" s="33">
+      <c r="J29" s="34">
         <v>-52.58</v>
       </c>
-      <c r="K29" s="33">
+      <c r="K29" s="34">
         <v>-185.82</v>
       </c>
-      <c r="L29" s="33">
+      <c r="L29" s="34">
         <v>-194.78</v>
       </c>
-      <c r="M29" s="33">
+      <c r="M29" s="34">
         <v>-357.42</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="33">
         <v>42.03</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="33">
         <v>46.04</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="33">
         <v>13.37</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="33">
         <v>42.95</v>
       </c>
-      <c r="R29" s="33">
+      <c r="R29" s="34">
         <v>-162.27</v>
       </c>
-      <c r="S29" s="32"/>
+      <c r="S29" s="33"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="29" t="s">
+        <v>409</v>
+      </c>
+      <c r="B30" s="34">
         <v>-1.68</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>-10.16</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>-8.88</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>-7.41</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>-16.73</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>-41.12</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>-80.97</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>-183.93</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>-118.04</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>-78.28</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>-41.47</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>-13.59</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>-2.33</v>
       </c>
-      <c r="O30" s="32"/>
-      <c r="P30" s="32"/>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="32"/>
-      <c r="S30" s="32"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
+      <c r="A31" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>410</v>
-      </c>
-      <c r="B32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="Q32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="R32" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="S32" s="32"/>
+      <c r="A32" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="B32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="Q32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="R32" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="S32" s="33"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>411</v>
-      </c>
-      <c r="B33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="32"/>
+      <c r="A33" s="29" t="s">
+        <v>412</v>
+      </c>
+      <c r="B33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="J33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="B34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="R34" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="S34" s="32"/>
+      <c r="A34" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="B34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="D34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="R34" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="S34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>413</v>
-      </c>
-      <c r="B35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="32"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
+      <c r="A35" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="B35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
+      <c r="A36" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="B37" s="30">
+      <c r="A37" s="29" t="s">
+        <v>416</v>
+      </c>
+      <c r="B37" s="31">
         <v>2.07</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <v>1.17</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <v>1.06</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <v>1.06</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <v>2.83</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="31">
         <v>2.25</v>
       </c>
-      <c r="H37" s="30">
+      <c r="H37" s="31">
         <v>0.93</v>
       </c>
-      <c r="I37" s="30">
+      <c r="I37" s="31">
         <v>0.92</v>
       </c>
-      <c r="J37" s="30">
+      <c r="J37" s="31">
         <v>0.88</v>
       </c>
-      <c r="K37" s="30">
+      <c r="K37" s="31">
         <v>0.78</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="31">
         <v>0.64</v>
       </c>
-      <c r="M37" s="30">
+      <c r="M37" s="31">
         <v>0.38</v>
       </c>
-      <c r="N37" s="30">
+      <c r="N37" s="31">
         <v>0.46</v>
       </c>
-      <c r="O37" s="30">
+      <c r="O37" s="31">
         <v>0.22</v>
       </c>
-      <c r="P37" s="30">
+      <c r="P37" s="31">
         <v>0.33</v>
       </c>
-      <c r="Q37" s="30">
+      <c r="Q37" s="31">
         <v>0.2</v>
       </c>
-      <c r="R37" s="30">
+      <c r="R37" s="31">
         <v>0.2</v>
       </c>
-      <c r="S37" s="31"/>
+      <c r="S37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="B38" s="30">
+      <c r="A38" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="B38" s="31">
         <v>1.56</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <v>1.56</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <v>1.4</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <v>1.24</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <v>1.14</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="31">
         <v>0.98</v>
       </c>
-      <c r="H38" s="30">
+      <c r="H38" s="31">
         <v>0.81</v>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="31">
         <v>0.58</v>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="31">
         <v>0.5</v>
       </c>
-      <c r="K38" s="30">
+      <c r="K38" s="31">
         <v>0.35</v>
       </c>
-      <c r="L38" s="30">
+      <c r="L38" s="31">
         <v>0.34</v>
       </c>
-      <c r="M38" s="30">
+      <c r="M38" s="31">
         <v>0.29</v>
       </c>
-      <c r="N38" s="30">
+      <c r="N38" s="31">
         <v>0.26</v>
       </c>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="31"/>
-      <c r="S38" s="31"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="26" t="s">
-        <v>417</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
+      <c r="A39" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="30">
+      <c r="A40" s="29" t="s">
+        <v>419</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="31">
         <v>6.77</v>
       </c>
-      <c r="I40" s="30">
+      <c r="I40" s="31">
         <v>2.04</v>
       </c>
-      <c r="J40" s="30">
+      <c r="J40" s="31">
         <v>2.18</v>
       </c>
-      <c r="K40" s="31"/>
-      <c r="L40" s="30">
+      <c r="K40" s="32"/>
+      <c r="L40" s="31">
         <v>1.66</v>
       </c>
-      <c r="M40" s="30">
+      <c r="M40" s="31">
         <v>0.5</v>
       </c>
-      <c r="N40" s="31"/>
-      <c r="O40" s="30">
+      <c r="N40" s="32"/>
+      <c r="O40" s="31">
         <v>0.84</v>
       </c>
-      <c r="P40" s="30">
+      <c r="P40" s="31">
         <v>1.35</v>
       </c>
-      <c r="Q40" s="30">
+      <c r="Q40" s="31">
         <v>1.2</v>
       </c>
-      <c r="R40" s="30">
+      <c r="R40" s="31">
         <v>3.34</v>
       </c>
-      <c r="S40" s="31"/>
+      <c r="S40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>419</v>
-      </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="30">
+      <c r="A41" s="29" t="s">
+        <v>420</v>
+      </c>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="31">
         <v>7.65</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <v>4.01</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41" s="31">
         <v>4.7</v>
       </c>
-      <c r="H41" s="30">
+      <c r="H41" s="31">
         <v>2.96</v>
       </c>
-      <c r="I41" s="30">
+      <c r="I41" s="31">
         <v>1.09</v>
       </c>
-      <c r="J41" s="30">
+      <c r="J41" s="31">
         <v>1.78</v>
       </c>
-      <c r="K41" s="30">
+      <c r="K41" s="31">
         <v>1.32</v>
       </c>
-      <c r="L41" s="30">
+      <c r="L41" s="31">
         <v>1.25</v>
       </c>
-      <c r="M41" s="30">
+      <c r="M41" s="31">
         <v>1.22</v>
       </c>
-      <c r="N41" s="30">
+      <c r="N41" s="31">
         <v>1.68</v>
       </c>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="31"/>
-      <c r="S41" s="31"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32"/>
+      <c r="S41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
+      <c r="A42" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>421</v>
-      </c>
-      <c r="B43" s="30">
+      <c r="A43" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="B43" s="31">
         <v>0.94</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <v>0.63</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <v>0.38</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>0.38</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>1.43</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="31">
         <v>0.69</v>
       </c>
-      <c r="H43" s="30">
+      <c r="H43" s="31">
         <v>0.52</v>
       </c>
-      <c r="I43" s="30">
+      <c r="I43" s="31">
         <v>0.62</v>
       </c>
-      <c r="J43" s="30">
+      <c r="J43" s="31">
         <v>0.63</v>
       </c>
-      <c r="K43" s="30">
+      <c r="K43" s="31">
         <v>0.3</v>
       </c>
-      <c r="L43" s="30">
+      <c r="L43" s="31">
         <v>0.16</v>
       </c>
-      <c r="M43" s="30">
+      <c r="M43" s="31">
         <v>0.19</v>
       </c>
-      <c r="N43" s="30">
+      <c r="N43" s="31">
         <v>0.18</v>
       </c>
-      <c r="O43" s="30">
+      <c r="O43" s="31">
         <v>0.09</v>
       </c>
-      <c r="P43" s="30">
+      <c r="P43" s="31">
         <v>0.16</v>
       </c>
-      <c r="Q43" s="30">
+      <c r="Q43" s="31">
         <v>0.06</v>
       </c>
-      <c r="R43" s="30">
+      <c r="R43" s="31">
         <v>0.07</v>
       </c>
-      <c r="S43" s="31"/>
+      <c r="S43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="B44" s="30">
+      <c r="A44" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="B44" s="31">
         <v>0.66</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <v>0.61</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <v>0.58</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="31">
         <v>0.63</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="31">
         <v>0.67</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="31">
         <v>0.54</v>
       </c>
-      <c r="H44" s="30">
+      <c r="H44" s="31">
         <v>0.33</v>
       </c>
-      <c r="I44" s="30">
+      <c r="I44" s="31">
         <v>0.26</v>
       </c>
-      <c r="J44" s="30">
+      <c r="J44" s="31">
         <v>0.21</v>
       </c>
-      <c r="K44" s="30">
+      <c r="K44" s="31">
         <v>0.14</v>
       </c>
-      <c r="L44" s="30">
+      <c r="L44" s="31">
         <v>0.14</v>
       </c>
-      <c r="M44" s="30">
+      <c r="M44" s="31">
         <v>0.11</v>
       </c>
-      <c r="N44" s="30">
+      <c r="N44" s="31">
         <v>0.1</v>
       </c>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="31"/>
-      <c r="S44" s="31"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="27"/>
-      <c r="Q45" s="27"/>
-      <c r="R45" s="27"/>
-      <c r="S45" s="27"/>
+      <c r="A45" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>424</v>
-      </c>
-      <c r="B46" s="30">
+      <c r="A46" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="B46" s="31">
         <v>7.47</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="30">
         <v>818.16</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="31">
         <v>6.76</v>
       </c>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="30">
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="31">
         <v>70.9</v>
       </c>
-      <c r="I46" s="30">
+      <c r="I46" s="31">
         <v>21.88</v>
       </c>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="30">
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="31">
         <v>2.38</v>
       </c>
-      <c r="O46" s="30">
+      <c r="O46" s="31">
         <v>2.17</v>
       </c>
-      <c r="P46" s="30">
+      <c r="P46" s="31">
         <v>7.48</v>
       </c>
-      <c r="Q46" s="30">
+      <c r="Q46" s="31">
         <v>2.33</v>
       </c>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="26" t="s">
-        <v>425</v>
-      </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
+      <c r="A47" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>426</v>
-      </c>
-      <c r="B48" s="30">
+      <c r="A48" s="29" t="s">
+        <v>427</v>
+      </c>
+      <c r="B48" s="31">
         <v>9.79</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="31">
         <v>9.0</v>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="31">
         <v>6.19</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="31">
         <v>14.45</v>
       </c>
-      <c r="F48" s="31"/>
-      <c r="G48" s="30">
+      <c r="F48" s="32"/>
+      <c r="G48" s="31">
         <v>12.85</v>
       </c>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="30">
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="31">
         <v>2.22</v>
       </c>
-      <c r="P48" s="30">
+      <c r="P48" s="31">
         <v>4.79</v>
       </c>
-      <c r="Q48" s="30">
+      <c r="Q48" s="31">
         <v>1.3</v>
       </c>
-      <c r="R48" s="30">
+      <c r="R48" s="31">
         <v>2.74</v>
       </c>
-      <c r="S48" s="31"/>
+      <c r="S48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="B49" s="30">
+      <c r="A49" s="29" t="s">
+        <v>428</v>
+      </c>
+      <c r="B49" s="31">
         <v>14.59</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="31">
         <v>16.5</v>
       </c>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="31"/>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="31"/>
-      <c r="S49" s="31"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="27"/>
-      <c r="R50" s="27"/>
-      <c r="S50" s="27"/>
+      <c r="A50" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="28"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="B51" s="30">
+      <c r="A51" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="B51" s="31">
         <v>59.78</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="29">
+      <c r="C51" s="32"/>
+      <c r="D51" s="30">
         <v>104.75</v>
       </c>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="30">
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="31">
         <v>59.57</v>
       </c>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="31"/>
-      <c r="P51" s="30">
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="31">
         <v>43.6</v>
       </c>
-      <c r="Q51" s="30">
+      <c r="Q51" s="31">
         <v>3.92</v>
       </c>
-      <c r="R51" s="30">
+      <c r="R51" s="31">
         <v>14.2</v>
       </c>
-      <c r="S51" s="31"/>
+      <c r="S51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>431</v>
-      </c>
-      <c r="B53" s="30">
+      <c r="A53" s="29" t="s">
+        <v>432</v>
+      </c>
+      <c r="B53" s="31">
         <v>59.23</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="29">
+      <c r="C53" s="32"/>
+      <c r="D53" s="30">
         <v>104.75</v>
       </c>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="30">
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="31">
         <v>59.57</v>
       </c>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="30">
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="31">
         <v>3.8</v>
       </c>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="30">
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="31">
         <v>9.73</v>
       </c>
-      <c r="Q53" s="30">
+      <c r="Q53" s="31">
         <v>4.26</v>
       </c>
-      <c r="R53" s="30">
+      <c r="R53" s="31">
         <v>4.25</v>
       </c>
-      <c r="S53" s="31"/>
+      <c r="S53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>432</v>
-      </c>
-      <c r="B54" s="30">
+      <c r="A54" s="29" t="s">
+        <v>433</v>
+      </c>
+      <c r="B54" s="31">
         <v>1.56</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="31">
         <v>1.56</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="31">
         <v>1.4</v>
       </c>
-      <c r="E54" s="30">
+      <c r="E54" s="31">
         <v>1.24</v>
       </c>
-      <c r="F54" s="30">
+      <c r="F54" s="31">
         <v>1.14</v>
       </c>
-      <c r="G54" s="30">
+      <c r="G54" s="31">
         <v>0.98</v>
       </c>
-      <c r="H54" s="30">
+      <c r="H54" s="31">
         <v>0.81</v>
       </c>
-      <c r="I54" s="30">
+      <c r="I54" s="31">
         <v>0.58</v>
       </c>
-      <c r="J54" s="30">
+      <c r="J54" s="31">
         <v>0.5</v>
       </c>
-      <c r="K54" s="30">
+      <c r="K54" s="31">
         <v>0.35</v>
       </c>
-      <c r="L54" s="30">
+      <c r="L54" s="31">
         <v>0.34</v>
       </c>
-      <c r="M54" s="30">
+      <c r="M54" s="31">
         <v>0.29</v>
       </c>
-      <c r="N54" s="30">
+      <c r="N54" s="31">
         <v>0.26</v>
       </c>
-      <c r="O54" s="31"/>
-      <c r="P54" s="31"/>
-      <c r="Q54" s="31"/>
-      <c r="R54" s="31"/>
-      <c r="S54" s="31"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="B56" s="30">
+      <c r="A56" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="B56" s="31">
         <v>0.25</v>
       </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="30">
+      <c r="C56" s="32"/>
+      <c r="D56" s="31">
         <v>0.95</v>
       </c>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="30">
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="31">
         <v>0.58</v>
       </c>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="31"/>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-      <c r="N56" s="31"/>
-      <c r="O56" s="31"/>
-      <c r="P56" s="34">
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="35">
         <v>-0.5</v>
       </c>
-      <c r="Q56" s="30">
+      <c r="Q56" s="31">
         <v>0.01</v>
       </c>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
+      <c r="A57" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="28"/>
+      <c r="R57" s="28"/>
+      <c r="S57" s="28"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>436</v>
-      </c>
-      <c r="B58" s="30">
+      <c r="A58" s="29" t="s">
+        <v>437</v>
+      </c>
+      <c r="B58" s="31">
         <v>1.22</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C58" s="31">
         <v>1.18</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="31">
         <v>0.62</v>
       </c>
-      <c r="E58" s="30">
+      <c r="E58" s="31">
         <v>0.82</v>
       </c>
-      <c r="F58" s="30">
+      <c r="F58" s="31">
         <v>4.15</v>
       </c>
-      <c r="G58" s="30">
+      <c r="G58" s="31">
         <v>0.97</v>
       </c>
-      <c r="H58" s="30">
+      <c r="H58" s="31">
         <v>0.58</v>
       </c>
-      <c r="I58" s="30">
+      <c r="I58" s="31">
         <v>0.46</v>
       </c>
-      <c r="J58" s="30">
+      <c r="J58" s="31">
         <v>0.44</v>
       </c>
-      <c r="K58" s="30">
+      <c r="K58" s="31">
         <v>0.46</v>
       </c>
-      <c r="L58" s="30">
+      <c r="L58" s="31">
         <v>0.31</v>
       </c>
-      <c r="M58" s="30">
+      <c r="M58" s="31">
         <v>0.94</v>
       </c>
-      <c r="N58" s="30">
+      <c r="N58" s="31">
         <v>0.73</v>
       </c>
-      <c r="O58" s="30">
+      <c r="O58" s="31">
         <v>0.32</v>
       </c>
-      <c r="P58" s="30">
+      <c r="P58" s="31">
         <v>0.26</v>
       </c>
-      <c r="Q58" s="30">
+      <c r="Q58" s="31">
         <v>0.29</v>
       </c>
-      <c r="R58" s="30">
+      <c r="R58" s="31">
         <v>0.32</v>
       </c>
-      <c r="S58" s="31"/>
+      <c r="S58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>437</v>
-      </c>
-      <c r="B59" s="30">
+      <c r="A59" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="B59" s="31">
         <v>1.05</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C59" s="31">
         <v>0.98</v>
       </c>
-      <c r="D59" s="30">
+      <c r="D59" s="31">
         <v>0.89</v>
       </c>
-      <c r="E59" s="30">
+      <c r="E59" s="31">
         <v>1.07</v>
       </c>
-      <c r="F59" s="30">
+      <c r="F59" s="31">
         <v>1.34</v>
       </c>
-      <c r="G59" s="30">
+      <c r="G59" s="31">
         <v>0.61</v>
       </c>
-      <c r="H59" s="30">
+      <c r="H59" s="31">
         <v>0.4</v>
       </c>
-      <c r="I59" s="30">
+      <c r="I59" s="31">
         <v>0.62</v>
       </c>
-      <c r="J59" s="30">
+      <c r="J59" s="31">
         <v>0.68</v>
       </c>
-      <c r="K59" s="30">
+      <c r="K59" s="31">
         <v>0.52</v>
       </c>
-      <c r="L59" s="30">
+      <c r="L59" s="31">
         <v>0.44</v>
       </c>
-      <c r="M59" s="30">
+      <c r="M59" s="31">
         <v>0.39</v>
       </c>
-      <c r="N59" s="30">
+      <c r="N59" s="31">
         <v>0.34</v>
       </c>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
+      <c r="A60" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="28"/>
+      <c r="P60" s="28"/>
+      <c r="Q60" s="28"/>
+      <c r="R60" s="28"/>
+      <c r="S60" s="28"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>439</v>
-      </c>
-      <c r="B61" s="30">
+      <c r="A61" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="B61" s="31">
         <v>9.15</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="31">
         <v>9.3</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="31">
         <v>6.4</v>
       </c>
-      <c r="E61" s="30">
+      <c r="E61" s="31">
         <v>11.82</v>
       </c>
-      <c r="F61" s="31"/>
-      <c r="G61" s="30">
+      <c r="F61" s="32"/>
+      <c r="G61" s="31">
         <v>13.39</v>
       </c>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="30">
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="31">
         <v>27.07</v>
       </c>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="30">
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="31">
         <v>9.45</v>
       </c>
-      <c r="N61" s="31"/>
-      <c r="O61" s="30">
+      <c r="N61" s="32"/>
+      <c r="O61" s="31">
         <v>5.5</v>
       </c>
-      <c r="P61" s="30">
+      <c r="P61" s="31">
         <v>3.6</v>
       </c>
-      <c r="Q61" s="30">
+      <c r="Q61" s="31">
         <v>3.56</v>
       </c>
-      <c r="R61" s="30">
+      <c r="R61" s="31">
         <v>5.08</v>
       </c>
-      <c r="S61" s="31"/>
+      <c r="S61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="B62" s="30">
+      <c r="A62" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="B62" s="31">
         <v>10.12</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C62" s="31">
         <v>10.8</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="31">
         <v>13.46</v>
       </c>
-      <c r="E62" s="30">
+      <c r="E62" s="31">
         <v>31.03</v>
       </c>
-      <c r="F62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="30">
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="31">
         <v>21.26</v>
       </c>
-      <c r="J62" s="31"/>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="29">
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="30">
         <v>113.75</v>
       </c>
-      <c r="N62" s="30">
+      <c r="N62" s="31">
         <v>34.7</v>
       </c>
-      <c r="O62" s="31"/>
-      <c r="P62" s="31"/>
-      <c r="Q62" s="31"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="31"/>
+      <c r="O62" s="32"/>
+      <c r="P62" s="32"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
-      <c r="S63" s="27"/>
+      <c r="A63" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="28"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>442</v>
-      </c>
-      <c r="B64" s="30">
+      <c r="A64" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="B64" s="31">
         <v>8.31</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C64" s="31">
         <v>54.58</v>
       </c>
-      <c r="D64" s="30">
+      <c r="D64" s="31">
         <v>8.22</v>
       </c>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="30">
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="31">
         <v>41.84</v>
       </c>
-      <c r="I64" s="30">
+      <c r="I64" s="31">
         <v>12.0</v>
       </c>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="30">
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="31">
         <v>9.69</v>
       </c>
-      <c r="O64" s="30">
+      <c r="O64" s="31">
         <v>6.56</v>
       </c>
-      <c r="P64" s="30">
+      <c r="P64" s="31">
         <v>7.4</v>
       </c>
-      <c r="Q64" s="30">
+      <c r="Q64" s="31">
         <v>5.82</v>
       </c>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="B65" s="30">
+      <c r="A65" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="B65" s="31">
         <v>21.44</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="30">
         <v>277.18</v>
       </c>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="30">
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32"/>
+      <c r="N65" s="31">
         <v>13.57</v>
       </c>
-      <c r="O65" s="31"/>
-      <c r="P65" s="31"/>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="31"/>
+      <c r="O65" s="32"/>
+      <c r="P65" s="32"/>
+      <c r="Q65" s="32"/>
+      <c r="R65" s="32"/>
+      <c r="S65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="26" t="s">
-        <v>444</v>
-      </c>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="27"/>
-      <c r="K66" s="27"/>
-      <c r="L66" s="27"/>
-      <c r="M66" s="27"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="27"/>
-      <c r="S66" s="27"/>
+      <c r="A66" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28"/>
+      <c r="J66" s="28"/>
+      <c r="K66" s="28"/>
+      <c r="L66" s="28"/>
+      <c r="M66" s="28"/>
+      <c r="N66" s="28"/>
+      <c r="O66" s="28"/>
+      <c r="P66" s="28"/>
+      <c r="Q66" s="28"/>
+      <c r="R66" s="28"/>
+      <c r="S66" s="28"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="B67" s="30">
+      <c r="A67" s="29" t="s">
+        <v>446</v>
+      </c>
+      <c r="B67" s="31">
         <v>9.71</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="30">
         <v>1546.42</v>
       </c>
-      <c r="D67" s="30">
+      <c r="D67" s="31">
         <v>10.94</v>
       </c>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="30">
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="31">
         <v>78.04</v>
       </c>
-      <c r="I67" s="30">
+      <c r="I67" s="31">
         <v>16.04</v>
       </c>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="30">
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="31">
         <v>9.69</v>
       </c>
-      <c r="O67" s="30">
+      <c r="O67" s="31">
         <v>7.88</v>
       </c>
-      <c r="P67" s="30">
+      <c r="P67" s="31">
         <v>12.28</v>
       </c>
-      <c r="Q67" s="30">
+      <c r="Q67" s="31">
         <v>10.4</v>
       </c>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>446</v>
-      </c>
-      <c r="B68" s="30">
+      <c r="A68" s="29" t="s">
+        <v>447</v>
+      </c>
+      <c r="B68" s="31">
         <v>51.21</v>
       </c>
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="31"/>
-      <c r="J68" s="31"/>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
-      <c r="N68" s="30">
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
+      <c r="L68" s="32"/>
+      <c r="M68" s="32"/>
+      <c r="N68" s="31">
         <v>82.6</v>
       </c>
-      <c r="O68" s="31"/>
-      <c r="P68" s="31"/>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="31"/>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="32"/>
     </row>
     <row r="69" ht="15.75" customHeight="1"/>
     <row r="70" ht="15.75" customHeight="1"/>
